--- a/AtchisonRegime/Outputs/USA/USA_Quality/df_regSummary_USA_Quality.xlsx
+++ b/AtchisonRegime/Outputs/USA/USA_Quality/df_regSummary_USA_Quality.xlsx
@@ -530,37 +530,37 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G2" t="n">
-        <v>1.611249289018029</v>
+        <v>1.374051827623967</v>
       </c>
       <c r="H2" t="n">
-        <v>3.343978758250776</v>
+        <v>3.758934545501023</v>
       </c>
       <c r="I2" t="n">
-        <v>-6.02684421181042</v>
+        <v>-11.6718085490494</v>
       </c>
       <c r="J2" t="n">
         <v>8.538804320682219</v>
       </c>
       <c r="K2" t="n">
-        <v>38.73239436619718</v>
+        <v>39.16083916083916</v>
       </c>
       <c r="L2" t="n">
         <v>5</v>
       </c>
       <c r="M2" t="n">
-        <v>11</v>
+        <v>11.2</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1956956467076387</v>
+        <v>0.1627384891323143</v>
       </c>
       <c r="O2" t="n">
         <v>-0.01060235851672997</v>
       </c>
       <c r="P2" t="n">
-        <v>0.4118273717747234</v>
+        <v>0.337710289520283</v>
       </c>
     </row>
     <row r="3">
@@ -603,7 +603,7 @@
         <v>8.076570009882129</v>
       </c>
       <c r="K3" t="n">
-        <v>18.30985915492958</v>
+        <v>18.18181818181818</v>
       </c>
       <c r="L3" t="n">
         <v>4</v>
@@ -661,7 +661,7 @@
         <v>7.72617150656165</v>
       </c>
       <c r="K4" t="n">
-        <v>20.42253521126761</v>
+        <v>20.27972027972028</v>
       </c>
       <c r="L4" t="n">
         <v>3</v>
@@ -719,7 +719,7 @@
         <v>7.69497967124499</v>
       </c>
       <c r="K5" t="n">
-        <v>22.53521126760564</v>
+        <v>22.37762237762238</v>
       </c>
       <c r="L5" t="n">
         <v>3</v>
